--- a/QuestionBank.xlsx
+++ b/QuestionBank.xlsx
@@ -1401,8 +1401,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Total Time: 10/20 Minutes | Total Marks: 10/20 Marks
-Instructions: Answer all sub-questions carefully.</t>
+          <t>Instructions: Answer all sub-questions carefully.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -3393,8 +3392,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Total Time: 10/20 Minutes | Total Marks: 10/20 Marks
-Instructions: Answer all sub-questions carefully.</t>
+          <t>Instructions: Answer all sub-questions carefully.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -5240,8 +5238,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Total Time: 10/20 Minutes | Total Marks: 10/20 Marks
-Instructions: Answer all sub-questions carefully.</t>
+          <t>Instructions: Answer all sub-questions carefully.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -7231,8 +7228,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Total Time: 10/20 Minutes | Total Marks: 10/20 Marks
-Instructions: Answer all sub-questions carefully.</t>
+          <t>Instructions: Answer all sub-questions carefully.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -9317,7 +9313,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -9333,7 +9329,7 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -9346,7 +9342,7 @@
         </is>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -9406,7 +9402,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -9422,7 +9418,7 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -9435,7 +9431,7 @@
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -9495,7 +9491,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -9511,7 +9507,7 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -9524,7 +9520,7 @@
         </is>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -9584,7 +9580,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -9600,7 +9596,7 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -9613,7 +9609,7 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -9673,7 +9669,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -9689,7 +9685,7 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -9702,7 +9698,7 @@
         </is>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -9762,7 +9758,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -9778,7 +9774,7 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -9791,7 +9787,7 @@
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -9851,7 +9847,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -9867,7 +9863,7 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -9880,7 +9876,7 @@
         </is>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -9940,7 +9936,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -9956,7 +9952,7 @@
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -9969,7 +9965,7 @@
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -10029,7 +10025,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -10045,7 +10041,7 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -10058,7 +10054,7 @@
         </is>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -10118,7 +10114,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -10134,7 +10130,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10143,7 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -10207,7 +10203,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -10223,7 +10219,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -10236,7 +10232,7 @@
         </is>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -10365,7 +10361,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10377,7 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -10394,7 +10390,7 @@
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -10454,7 +10450,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -10470,7 +10466,7 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -10483,7 +10479,7 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -10543,7 +10539,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -10559,7 +10555,7 @@
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -10572,7 +10568,7 @@
         </is>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -10632,7 +10628,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -10648,7 +10644,7 @@
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10657,7 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -10721,7 +10717,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -10737,7 +10733,7 @@
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10746,7 @@
         </is>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -10810,7 +10806,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -10826,7 +10822,7 @@
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -10839,7 +10835,7 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -10899,7 +10895,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -10915,7 +10911,7 @@
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -10928,7 +10924,7 @@
         </is>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -10988,7 +10984,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -11004,7 +11000,7 @@
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -11017,7 +11013,7 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -11077,7 +11073,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -11093,7 +11089,7 @@
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -11106,7 +11102,7 @@
         </is>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -11166,7 +11162,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -11182,7 +11178,7 @@
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -11195,7 +11191,7 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -11255,7 +11251,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -11271,7 +11267,7 @@
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -11284,7 +11280,7 @@
         </is>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -11413,7 +11409,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -11429,7 +11425,7 @@
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11438,7 @@
         </is>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -11502,7 +11498,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -11518,7 +11514,7 @@
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -11531,7 +11527,7 @@
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -11591,7 +11587,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -11607,7 +11603,7 @@
         </is>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -11620,7 +11616,7 @@
         </is>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -11680,7 +11676,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -11696,7 +11692,7 @@
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -11709,7 +11705,7 @@
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -11769,7 +11765,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -11785,7 +11781,7 @@
         </is>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -11798,7 +11794,7 @@
         </is>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -11858,7 +11854,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -11874,7 +11870,7 @@
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -11887,7 +11883,7 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -11947,7 +11943,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -11963,7 +11959,7 @@
         </is>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -11976,7 +11972,7 @@
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -12036,7 +12032,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -12052,7 +12048,7 @@
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -12065,7 +12061,7 @@
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -12125,7 +12121,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -12141,7 +12137,7 @@
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -12154,7 +12150,7 @@
         </is>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -12214,7 +12210,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -12230,7 +12226,7 @@
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -12243,7 +12239,7 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12299,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -12319,7 +12315,7 @@
         </is>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -12332,7 +12328,7 @@
         </is>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -12461,7 +12457,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -12477,7 +12473,7 @@
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -12490,7 +12486,7 @@
         </is>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -12550,7 +12546,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -12566,7 +12562,7 @@
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -12579,7 +12575,7 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -12639,7 +12635,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -12655,7 +12651,7 @@
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -12668,7 +12664,7 @@
         </is>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -12728,7 +12724,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -12744,7 +12740,7 @@
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -12757,7 +12753,7 @@
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -12817,7 +12813,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -12833,7 +12829,7 @@
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -12846,7 +12842,7 @@
         </is>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -12906,7 +12902,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -12922,7 +12918,7 @@
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -12935,7 +12931,7 @@
         </is>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -12995,7 +12991,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -13011,7 +13007,7 @@
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -13024,7 +13020,7 @@
         </is>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -13084,7 +13080,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -13100,7 +13096,7 @@
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -13113,7 +13109,7 @@
         </is>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -13173,7 +13169,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -13189,7 +13185,7 @@
         </is>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -13202,7 +13198,7 @@
         </is>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
@@ -13262,7 +13258,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -13278,7 +13274,7 @@
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -13291,7 +13287,7 @@
         </is>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -13351,7 +13347,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -13367,7 +13363,7 @@
         </is>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -13380,7 +13376,7 @@
         </is>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
@@ -13509,7 +13505,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -13525,7 +13521,7 @@
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -13538,7 +13534,7 @@
         </is>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
@@ -13598,7 +13594,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -13614,7 +13610,7 @@
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -13627,7 +13623,7 @@
         </is>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
@@ -13687,7 +13683,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -13703,7 +13699,7 @@
         </is>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -13716,7 +13712,7 @@
         </is>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
@@ -13776,7 +13772,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -13792,7 +13788,7 @@
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -13805,7 +13801,7 @@
         </is>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
@@ -13865,7 +13861,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -13881,7 +13877,7 @@
         </is>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -13894,7 +13890,7 @@
         </is>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
@@ -13954,7 +13950,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -13970,7 +13966,7 @@
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -13983,7 +13979,7 @@
         </is>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
@@ -14043,7 +14039,7 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -14059,7 +14055,7 @@
         </is>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -14072,7 +14068,7 @@
         </is>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
@@ -14132,7 +14128,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -14148,7 +14144,7 @@
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -14161,7 +14157,7 @@
         </is>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
@@ -14221,7 +14217,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -14237,7 +14233,7 @@
         </is>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -14250,7 +14246,7 @@
         </is>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -14310,7 +14306,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -14326,7 +14322,7 @@
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -14339,7 +14335,7 @@
         </is>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
@@ -14399,7 +14395,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -14415,7 +14411,7 @@
         </is>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -14428,7 +14424,7 @@
         </is>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
@@ -14557,7 +14553,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -14573,7 +14569,7 @@
         </is>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -14586,7 +14582,7 @@
         </is>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
@@ -14646,7 +14642,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -14662,7 +14658,7 @@
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -14675,7 +14671,7 @@
         </is>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
@@ -14735,7 +14731,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -14751,7 +14747,7 @@
         </is>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -14764,7 +14760,7 @@
         </is>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
@@ -14824,7 +14820,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -14840,7 +14836,7 @@
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -14853,7 +14849,7 @@
         </is>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
@@ -14913,7 +14909,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -14929,7 +14925,7 @@
         </is>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -14942,7 +14938,7 @@
         </is>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
@@ -15002,7 +14998,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -15018,7 +15014,7 @@
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -15031,7 +15027,7 @@
         </is>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
@@ -15091,7 +15087,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -15107,7 +15103,7 @@
         </is>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -15120,7 +15116,7 @@
         </is>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
@@ -15180,7 +15176,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -15196,7 +15192,7 @@
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -15209,7 +15205,7 @@
         </is>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
@@ -15269,7 +15265,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -15285,7 +15281,7 @@
         </is>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -15298,7 +15294,7 @@
         </is>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
@@ -15358,7 +15354,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -15374,7 +15370,7 @@
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -15387,7 +15383,7 @@
         </is>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
@@ -15447,7 +15443,7 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -15463,7 +15459,7 @@
         </is>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -15476,7 +15472,7 @@
         </is>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
@@ -15605,7 +15601,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -15621,7 +15617,7 @@
         </is>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -15634,7 +15630,7 @@
         </is>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
@@ -15694,7 +15690,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -15710,7 +15706,7 @@
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -15723,7 +15719,7 @@
         </is>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
@@ -15783,7 +15779,7 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -15799,7 +15795,7 @@
         </is>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -15812,7 +15808,7 @@
         </is>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
@@ -15872,7 +15868,7 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -15888,7 +15884,7 @@
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -15901,7 +15897,7 @@
         </is>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
@@ -15961,7 +15957,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -15977,7 +15973,7 @@
         </is>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -15990,7 +15986,7 @@
         </is>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
@@ -16050,7 +16046,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -16066,7 +16062,7 @@
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -16079,7 +16075,7 @@
         </is>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
@@ -16139,7 +16135,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -16155,7 +16151,7 @@
         </is>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -16168,7 +16164,7 @@
         </is>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
@@ -16228,7 +16224,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -16244,7 +16240,7 @@
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -16257,7 +16253,7 @@
         </is>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
@@ -16317,7 +16313,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -16333,7 +16329,7 @@
         </is>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -16346,7 +16342,7 @@
         </is>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
@@ -16406,7 +16402,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -16422,7 +16418,7 @@
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -16435,7 +16431,7 @@
         </is>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
@@ -16495,7 +16491,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -16511,7 +16507,7 @@
         </is>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -16524,7 +16520,7 @@
         </is>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
@@ -16653,7 +16649,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -16669,7 +16665,7 @@
         </is>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -16682,7 +16678,7 @@
         </is>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
@@ -16742,7 +16738,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -16758,7 +16754,7 @@
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -16771,7 +16767,7 @@
         </is>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
@@ -16831,7 +16827,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -16847,7 +16843,7 @@
         </is>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -16860,7 +16856,7 @@
         </is>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
@@ -16920,7 +16916,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -16936,7 +16932,7 @@
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -16949,7 +16945,7 @@
         </is>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
@@ -17009,7 +17005,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -17025,7 +17021,7 @@
         </is>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -17038,7 +17034,7 @@
         </is>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
@@ -17098,7 +17094,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -17114,7 +17110,7 @@
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -17127,7 +17123,7 @@
         </is>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
@@ -17187,7 +17183,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -17203,7 +17199,7 @@
         </is>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -17216,7 +17212,7 @@
         </is>
       </c>
       <c r="Q93" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
@@ -17276,7 +17272,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -17292,7 +17288,7 @@
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -17305,7 +17301,7 @@
         </is>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
@@ -17365,7 +17361,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -17381,7 +17377,7 @@
         </is>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -17394,7 +17390,7 @@
         </is>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
@@ -17454,7 +17450,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -17470,7 +17466,7 @@
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -17483,7 +17479,7 @@
         </is>
       </c>
       <c r="Q96" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
@@ -17543,7 +17539,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -17559,7 +17555,7 @@
         </is>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -17572,7 +17568,7 @@
         </is>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
@@ -17701,7 +17697,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -17717,7 +17713,7 @@
         </is>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -17730,7 +17726,7 @@
         </is>
       </c>
       <c r="Q99" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
@@ -17790,7 +17786,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -17806,7 +17802,7 @@
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -17819,7 +17815,7 @@
         </is>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
@@ -17879,7 +17875,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -17895,7 +17891,7 @@
         </is>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -17908,7 +17904,7 @@
         </is>
       </c>
       <c r="Q101" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
@@ -17968,7 +17964,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -17984,7 +17980,7 @@
         </is>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -17997,7 +17993,7 @@
         </is>
       </c>
       <c r="Q102" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
@@ -18057,7 +18053,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -18073,7 +18069,7 @@
         </is>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -18086,7 +18082,7 @@
         </is>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
@@ -18146,7 +18142,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -18162,7 +18158,7 @@
         </is>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -18175,7 +18171,7 @@
         </is>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
@@ -18235,7 +18231,7 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -18251,7 +18247,7 @@
         </is>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -18264,7 +18260,7 @@
         </is>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
@@ -18324,7 +18320,7 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -18340,7 +18336,7 @@
         </is>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -18353,7 +18349,7 @@
         </is>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
@@ -18413,7 +18409,7 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -18429,7 +18425,7 @@
         </is>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -18442,7 +18438,7 @@
         </is>
       </c>
       <c r="Q107" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
@@ -18502,7 +18498,7 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -18518,7 +18514,7 @@
         </is>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -18531,7 +18527,7 @@
         </is>
       </c>
       <c r="Q108" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
@@ -18591,7 +18587,7 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -18607,7 +18603,7 @@
         </is>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -18620,7 +18616,7 @@
         </is>
       </c>
       <c r="Q109" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
@@ -18749,7 +18745,7 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -18765,7 +18761,7 @@
         </is>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -18778,7 +18774,7 @@
         </is>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
@@ -18838,7 +18834,7 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -18854,7 +18850,7 @@
         </is>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -18867,7 +18863,7 @@
         </is>
       </c>
       <c r="Q112" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
@@ -18927,7 +18923,7 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -18943,7 +18939,7 @@
         </is>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -18956,7 +18952,7 @@
         </is>
       </c>
       <c r="Q113" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
@@ -19016,7 +19012,7 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -19032,7 +19028,7 @@
         </is>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -19045,7 +19041,7 @@
         </is>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
@@ -19105,7 +19101,7 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -19121,7 +19117,7 @@
         </is>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -19134,7 +19130,7 @@
         </is>
       </c>
       <c r="Q115" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
@@ -19194,7 +19190,7 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -19210,7 +19206,7 @@
         </is>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -19223,7 +19219,7 @@
         </is>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
@@ -19283,7 +19279,7 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -19299,7 +19295,7 @@
         </is>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -19312,7 +19308,7 @@
         </is>
       </c>
       <c r="Q117" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
@@ -19372,7 +19368,7 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -19388,7 +19384,7 @@
         </is>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -19401,7 +19397,7 @@
         </is>
       </c>
       <c r="Q118" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
@@ -19461,7 +19457,7 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -19477,7 +19473,7 @@
         </is>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -19490,7 +19486,7 @@
         </is>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
@@ -19550,7 +19546,7 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -19566,7 +19562,7 @@
         </is>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -19579,7 +19575,7 @@
         </is>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
@@ -19639,7 +19635,7 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -19655,7 +19651,7 @@
         </is>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -19668,7 +19664,7 @@
         </is>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
@@ -19797,7 +19793,7 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -19813,7 +19809,7 @@
         </is>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -19826,7 +19822,7 @@
         </is>
       </c>
       <c r="Q123" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
@@ -19886,7 +19882,7 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -19902,7 +19898,7 @@
         </is>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -19915,7 +19911,7 @@
         </is>
       </c>
       <c r="Q124" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
@@ -19975,7 +19971,7 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -19991,7 +19987,7 @@
         </is>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -20004,7 +20000,7 @@
         </is>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
@@ -20064,7 +20060,7 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -20080,7 +20076,7 @@
         </is>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -20093,7 +20089,7 @@
         </is>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
@@ -20153,7 +20149,7 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -20169,7 +20165,7 @@
         </is>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -20182,7 +20178,7 @@
         </is>
       </c>
       <c r="Q127" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
@@ -20242,7 +20238,7 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -20258,7 +20254,7 @@
         </is>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -20271,7 +20267,7 @@
         </is>
       </c>
       <c r="Q128" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
@@ -20331,7 +20327,7 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
@@ -20347,7 +20343,7 @@
         </is>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -20360,7 +20356,7 @@
         </is>
       </c>
       <c r="Q129" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
@@ -20420,7 +20416,7 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -20436,7 +20432,7 @@
         </is>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -20449,7 +20445,7 @@
         </is>
       </c>
       <c r="Q130" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
@@ -20509,7 +20505,7 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -20525,7 +20521,7 @@
         </is>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -20538,7 +20534,7 @@
         </is>
       </c>
       <c r="Q131" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
@@ -20598,7 +20594,7 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -20614,7 +20610,7 @@
         </is>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -20627,7 +20623,7 @@
         </is>
       </c>
       <c r="Q132" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
@@ -20687,7 +20683,7 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -20703,7 +20699,7 @@
         </is>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -20716,7 +20712,7 @@
         </is>
       </c>
       <c r="Q133" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
@@ -20845,7 +20841,7 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -20861,7 +20857,7 @@
         </is>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -20874,7 +20870,7 @@
         </is>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
@@ -20934,7 +20930,7 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -20950,7 +20946,7 @@
         </is>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -20963,7 +20959,7 @@
         </is>
       </c>
       <c r="Q136" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
@@ -21023,7 +21019,7 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -21039,7 +21035,7 @@
         </is>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -21052,7 +21048,7 @@
         </is>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
@@ -21112,7 +21108,7 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -21128,7 +21124,7 @@
         </is>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -21141,7 +21137,7 @@
         </is>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
@@ -21201,7 +21197,7 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -21217,7 +21213,7 @@
         </is>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -21230,7 +21226,7 @@
         </is>
       </c>
       <c r="Q139" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
@@ -21290,7 +21286,7 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -21306,7 +21302,7 @@
         </is>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -21319,7 +21315,7 @@
         </is>
       </c>
       <c r="Q140" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R140" s="2" t="inlineStr">
         <is>
@@ -21379,7 +21375,7 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -21395,7 +21391,7 @@
         </is>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -21408,7 +21404,7 @@
         </is>
       </c>
       <c r="Q141" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R141" s="2" t="inlineStr">
         <is>
@@ -21468,7 +21464,7 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -21484,7 +21480,7 @@
         </is>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -21497,7 +21493,7 @@
         </is>
       </c>
       <c r="Q142" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
@@ -21557,7 +21553,7 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -21573,7 +21569,7 @@
         </is>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -21586,7 +21582,7 @@
         </is>
       </c>
       <c r="Q143" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
@@ -21646,7 +21642,7 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -21662,7 +21658,7 @@
         </is>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -21675,7 +21671,7 @@
         </is>
       </c>
       <c r="Q144" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R144" s="2" t="inlineStr">
         <is>
@@ -21735,7 +21731,7 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -21751,7 +21747,7 @@
         </is>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -21764,7 +21760,7 @@
         </is>
       </c>
       <c r="Q145" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
@@ -21893,7 +21889,7 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -21909,7 +21905,7 @@
         </is>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -21922,7 +21918,7 @@
         </is>
       </c>
       <c r="Q147" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R147" s="2" t="inlineStr">
         <is>
@@ -21982,7 +21978,7 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -21998,7 +21994,7 @@
         </is>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -22011,7 +22007,7 @@
         </is>
       </c>
       <c r="Q148" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
@@ -22071,7 +22067,7 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -22087,7 +22083,7 @@
         </is>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -22100,7 +22096,7 @@
         </is>
       </c>
       <c r="Q149" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R149" s="2" t="inlineStr">
         <is>
@@ -22160,7 +22156,7 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -22176,7 +22172,7 @@
         </is>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -22189,7 +22185,7 @@
         </is>
       </c>
       <c r="Q150" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R150" s="2" t="inlineStr">
         <is>
@@ -22249,7 +22245,7 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -22265,7 +22261,7 @@
         </is>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -22278,7 +22274,7 @@
         </is>
       </c>
       <c r="Q151" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R151" s="2" t="inlineStr">
         <is>
@@ -22338,7 +22334,7 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -22354,7 +22350,7 @@
         </is>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -22367,7 +22363,7 @@
         </is>
       </c>
       <c r="Q152" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
@@ -22427,7 +22423,7 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -22443,7 +22439,7 @@
         </is>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -22456,7 +22452,7 @@
         </is>
       </c>
       <c r="Q153" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R153" s="2" t="inlineStr">
         <is>
@@ -22516,7 +22512,7 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -22532,7 +22528,7 @@
         </is>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -22545,7 +22541,7 @@
         </is>
       </c>
       <c r="Q154" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R154" s="2" t="inlineStr">
         <is>
@@ -22605,7 +22601,7 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -22621,7 +22617,7 @@
         </is>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -22634,7 +22630,7 @@
         </is>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R155" s="2" t="inlineStr">
         <is>
@@ -22694,7 +22690,7 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -22710,7 +22706,7 @@
         </is>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -22723,7 +22719,7 @@
         </is>
       </c>
       <c r="Q156" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
@@ -22783,7 +22779,7 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -22799,7 +22795,7 @@
         </is>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -22812,7 +22808,7 @@
         </is>
       </c>
       <c r="Q157" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R157" s="2" t="inlineStr">
         <is>
@@ -22941,7 +22937,7 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -22957,7 +22953,7 @@
         </is>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -22970,7 +22966,7 @@
         </is>
       </c>
       <c r="Q159" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R159" s="2" t="inlineStr">
         <is>
@@ -23030,7 +23026,7 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -23046,7 +23042,7 @@
         </is>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -23059,7 +23055,7 @@
         </is>
       </c>
       <c r="Q160" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R160" s="2" t="inlineStr">
         <is>
@@ -23119,7 +23115,7 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -23135,7 +23131,7 @@
         </is>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -23148,7 +23144,7 @@
         </is>
       </c>
       <c r="Q161" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R161" s="2" t="inlineStr">
         <is>
@@ -23208,7 +23204,7 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -23224,7 +23220,7 @@
         </is>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -23237,7 +23233,7 @@
         </is>
       </c>
       <c r="Q162" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
@@ -23297,7 +23293,7 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -23313,7 +23309,7 @@
         </is>
       </c>
       <c r="N163" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -23326,7 +23322,7 @@
         </is>
       </c>
       <c r="Q163" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R163" s="2" t="inlineStr">
         <is>
@@ -23386,7 +23382,7 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -23402,7 +23398,7 @@
         </is>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -23415,7 +23411,7 @@
         </is>
       </c>
       <c r="Q164" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R164" s="2" t="inlineStr">
         <is>
@@ -23475,7 +23471,7 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -23491,7 +23487,7 @@
         </is>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -23504,7 +23500,7 @@
         </is>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R165" s="2" t="inlineStr">
         <is>
@@ -23564,7 +23560,7 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -23580,7 +23576,7 @@
         </is>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -23593,7 +23589,7 @@
         </is>
       </c>
       <c r="Q166" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R166" s="2" t="inlineStr">
         <is>
@@ -23653,7 +23649,7 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -23669,7 +23665,7 @@
         </is>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -23682,7 +23678,7 @@
         </is>
       </c>
       <c r="Q167" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R167" s="2" t="inlineStr">
         <is>
@@ -23742,7 +23738,7 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -23758,7 +23754,7 @@
         </is>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -23771,7 +23767,7 @@
         </is>
       </c>
       <c r="Q168" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R168" s="2" t="inlineStr">
         <is>
@@ -23831,7 +23827,7 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
@@ -23847,7 +23843,7 @@
         </is>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -23860,7 +23856,7 @@
         </is>
       </c>
       <c r="Q169" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R169" s="2" t="inlineStr">
         <is>
@@ -23989,7 +23985,7 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -24005,7 +24001,7 @@
         </is>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -24018,7 +24014,7 @@
         </is>
       </c>
       <c r="Q171" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R171" s="2" t="inlineStr">
         <is>
@@ -24078,7 +24074,7 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -24094,7 +24090,7 @@
         </is>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -24107,7 +24103,7 @@
         </is>
       </c>
       <c r="Q172" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R172" s="2" t="inlineStr">
         <is>
@@ -24167,7 +24163,7 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -24183,7 +24179,7 @@
         </is>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -24196,7 +24192,7 @@
         </is>
       </c>
       <c r="Q173" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R173" s="2" t="inlineStr">
         <is>
@@ -24256,7 +24252,7 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -24272,7 +24268,7 @@
         </is>
       </c>
       <c r="N174" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -24285,7 +24281,7 @@
         </is>
       </c>
       <c r="Q174" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R174" s="2" t="inlineStr">
         <is>
@@ -24345,7 +24341,7 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -24361,7 +24357,7 @@
         </is>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -24374,7 +24370,7 @@
         </is>
       </c>
       <c r="Q175" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R175" s="2" t="inlineStr">
         <is>
@@ -24434,7 +24430,7 @@
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -24450,7 +24446,7 @@
         </is>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -24463,7 +24459,7 @@
         </is>
       </c>
       <c r="Q176" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R176" s="2" t="inlineStr">
         <is>
@@ -24523,7 +24519,7 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -24539,7 +24535,7 @@
         </is>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -24552,7 +24548,7 @@
         </is>
       </c>
       <c r="Q177" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R177" s="2" t="inlineStr">
         <is>
@@ -24612,7 +24608,7 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -24628,7 +24624,7 @@
         </is>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -24641,7 +24637,7 @@
         </is>
       </c>
       <c r="Q178" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R178" s="2" t="inlineStr">
         <is>
@@ -24701,7 +24697,7 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -24717,7 +24713,7 @@
         </is>
       </c>
       <c r="N179" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -24730,7 +24726,7 @@
         </is>
       </c>
       <c r="Q179" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R179" s="2" t="inlineStr">
         <is>
@@ -24790,7 +24786,7 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -24806,7 +24802,7 @@
         </is>
       </c>
       <c r="N180" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -24819,7 +24815,7 @@
         </is>
       </c>
       <c r="Q180" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R180" s="2" t="inlineStr">
         <is>
@@ -24879,7 +24875,7 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -24895,7 +24891,7 @@
         </is>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -24908,7 +24904,7 @@
         </is>
       </c>
       <c r="Q181" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R181" s="2" t="inlineStr">
         <is>
@@ -25037,7 +25033,7 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -25053,7 +25049,7 @@
         </is>
       </c>
       <c r="N183" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -25066,7 +25062,7 @@
         </is>
       </c>
       <c r="Q183" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R183" s="2" t="inlineStr">
         <is>
@@ -25126,7 +25122,7 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -25142,7 +25138,7 @@
         </is>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -25155,7 +25151,7 @@
         </is>
       </c>
       <c r="Q184" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R184" s="2" t="inlineStr">
         <is>
@@ -25215,7 +25211,7 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -25231,7 +25227,7 @@
         </is>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -25244,7 +25240,7 @@
         </is>
       </c>
       <c r="Q185" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R185" s="2" t="inlineStr">
         <is>
@@ -25304,7 +25300,7 @@
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -25320,7 +25316,7 @@
         </is>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -25333,7 +25329,7 @@
         </is>
       </c>
       <c r="Q186" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R186" s="2" t="inlineStr">
         <is>
@@ -25393,7 +25389,7 @@
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -25409,7 +25405,7 @@
         </is>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -25422,7 +25418,7 @@
         </is>
       </c>
       <c r="Q187" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R187" s="2" t="inlineStr">
         <is>
@@ -25482,7 +25478,7 @@
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -25498,7 +25494,7 @@
         </is>
       </c>
       <c r="N188" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -25511,7 +25507,7 @@
         </is>
       </c>
       <c r="Q188" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R188" s="2" t="inlineStr">
         <is>
@@ -25571,7 +25567,7 @@
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -25587,7 +25583,7 @@
         </is>
       </c>
       <c r="N189" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -25600,7 +25596,7 @@
         </is>
       </c>
       <c r="Q189" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R189" s="2" t="inlineStr">
         <is>
@@ -25660,7 +25656,7 @@
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -25676,7 +25672,7 @@
         </is>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -25689,7 +25685,7 @@
         </is>
       </c>
       <c r="Q190" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R190" s="2" t="inlineStr">
         <is>
@@ -25749,7 +25745,7 @@
         </is>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -25765,7 +25761,7 @@
         </is>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -25778,7 +25774,7 @@
         </is>
       </c>
       <c r="Q191" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R191" s="2" t="inlineStr">
         <is>
@@ -25838,7 +25834,7 @@
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -25854,7 +25850,7 @@
         </is>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -25867,7 +25863,7 @@
         </is>
       </c>
       <c r="Q192" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R192" s="2" t="inlineStr">
         <is>
@@ -25927,7 +25923,7 @@
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -25943,7 +25939,7 @@
         </is>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -25956,7 +25952,7 @@
         </is>
       </c>
       <c r="Q193" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R193" s="2" t="inlineStr">
         <is>
@@ -26085,7 +26081,7 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
@@ -26101,7 +26097,7 @@
         </is>
       </c>
       <c r="N195" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -26114,7 +26110,7 @@
         </is>
       </c>
       <c r="Q195" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R195" s="2" t="inlineStr">
         <is>
@@ -26174,7 +26170,7 @@
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -26190,7 +26186,7 @@
         </is>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -26203,7 +26199,7 @@
         </is>
       </c>
       <c r="Q196" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R196" s="2" t="inlineStr">
         <is>
@@ -26263,7 +26259,7 @@
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -26279,7 +26275,7 @@
         </is>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -26292,7 +26288,7 @@
         </is>
       </c>
       <c r="Q197" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R197" s="2" t="inlineStr">
         <is>
@@ -26352,7 +26348,7 @@
         </is>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -26368,7 +26364,7 @@
         </is>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -26381,7 +26377,7 @@
         </is>
       </c>
       <c r="Q198" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R198" s="2" t="inlineStr">
         <is>
@@ -26441,7 +26437,7 @@
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -26457,7 +26453,7 @@
         </is>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -26470,7 +26466,7 @@
         </is>
       </c>
       <c r="Q199" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R199" s="2" t="inlineStr">
         <is>
@@ -26530,7 +26526,7 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -26546,7 +26542,7 @@
         </is>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -26559,7 +26555,7 @@
         </is>
       </c>
       <c r="Q200" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R200" s="2" t="inlineStr">
         <is>
@@ -26619,7 +26615,7 @@
         </is>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -26635,7 +26631,7 @@
         </is>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -26648,7 +26644,7 @@
         </is>
       </c>
       <c r="Q201" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R201" s="2" t="inlineStr">
         <is>
@@ -26708,7 +26704,7 @@
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -26724,7 +26720,7 @@
         </is>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -26737,7 +26733,7 @@
         </is>
       </c>
       <c r="Q202" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R202" s="2" t="inlineStr">
         <is>
@@ -26797,7 +26793,7 @@
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -26813,7 +26809,7 @@
         </is>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -26826,7 +26822,7 @@
         </is>
       </c>
       <c r="Q203" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R203" s="2" t="inlineStr">
         <is>
@@ -26886,7 +26882,7 @@
         </is>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -26902,7 +26898,7 @@
         </is>
       </c>
       <c r="N204" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -26915,7 +26911,7 @@
         </is>
       </c>
       <c r="Q204" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R204" s="2" t="inlineStr">
         <is>
@@ -26975,7 +26971,7 @@
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -26991,7 +26987,7 @@
         </is>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -27004,7 +27000,7 @@
         </is>
       </c>
       <c r="Q205" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R205" s="2" t="inlineStr">
         <is>
@@ -27133,7 +27129,7 @@
         </is>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -27149,7 +27145,7 @@
         </is>
       </c>
       <c r="N207" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -27162,7 +27158,7 @@
         </is>
       </c>
       <c r="Q207" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R207" s="2" t="inlineStr">
         <is>
@@ -27222,7 +27218,7 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -27238,7 +27234,7 @@
         </is>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -27251,7 +27247,7 @@
         </is>
       </c>
       <c r="Q208" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R208" s="2" t="inlineStr">
         <is>
@@ -27311,7 +27307,7 @@
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -27327,7 +27323,7 @@
         </is>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -27340,7 +27336,7 @@
         </is>
       </c>
       <c r="Q209" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R209" s="2" t="inlineStr">
         <is>
@@ -27400,7 +27396,7 @@
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -27416,7 +27412,7 @@
         </is>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -27429,7 +27425,7 @@
         </is>
       </c>
       <c r="Q210" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R210" s="2" t="inlineStr">
         <is>
@@ -27489,7 +27485,7 @@
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -27505,7 +27501,7 @@
         </is>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -27518,7 +27514,7 @@
         </is>
       </c>
       <c r="Q211" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R211" s="2" t="inlineStr">
         <is>
@@ -27578,7 +27574,7 @@
         </is>
       </c>
       <c r="J212" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -27594,7 +27590,7 @@
         </is>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -27607,7 +27603,7 @@
         </is>
       </c>
       <c r="Q212" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R212" s="2" t="inlineStr">
         <is>
@@ -27667,7 +27663,7 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -27683,7 +27679,7 @@
         </is>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -27696,7 +27692,7 @@
         </is>
       </c>
       <c r="Q213" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R213" s="2" t="inlineStr">
         <is>
@@ -27756,7 +27752,7 @@
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -27772,7 +27768,7 @@
         </is>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -27785,7 +27781,7 @@
         </is>
       </c>
       <c r="Q214" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R214" s="2" t="inlineStr">
         <is>
@@ -27845,7 +27841,7 @@
         </is>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -27861,7 +27857,7 @@
         </is>
       </c>
       <c r="N215" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -27874,7 +27870,7 @@
         </is>
       </c>
       <c r="Q215" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R215" s="2" t="inlineStr">
         <is>
@@ -27934,7 +27930,7 @@
         </is>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -27950,7 +27946,7 @@
         </is>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -27963,7 +27959,7 @@
         </is>
       </c>
       <c r="Q216" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R216" s="2" t="inlineStr">
         <is>
@@ -28023,7 +28019,7 @@
         </is>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -28039,7 +28035,7 @@
         </is>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -28052,7 +28048,7 @@
         </is>
       </c>
       <c r="Q217" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R217" s="2" t="inlineStr">
         <is>
@@ -28181,7 +28177,7 @@
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -28197,7 +28193,7 @@
         </is>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -28210,7 +28206,7 @@
         </is>
       </c>
       <c r="Q219" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R219" s="2" t="inlineStr">
         <is>
@@ -28270,7 +28266,7 @@
         </is>
       </c>
       <c r="J220" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -28286,7 +28282,7 @@
         </is>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -28299,7 +28295,7 @@
         </is>
       </c>
       <c r="Q220" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R220" s="2" t="inlineStr">
         <is>
@@ -28359,7 +28355,7 @@
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -28375,7 +28371,7 @@
         </is>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -28388,7 +28384,7 @@
         </is>
       </c>
       <c r="Q221" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R221" s="2" t="inlineStr">
         <is>
@@ -28448,7 +28444,7 @@
         </is>
       </c>
       <c r="J222" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -28464,7 +28460,7 @@
         </is>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -28477,7 +28473,7 @@
         </is>
       </c>
       <c r="Q222" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R222" s="2" t="inlineStr">
         <is>
@@ -28537,7 +28533,7 @@
         </is>
       </c>
       <c r="J223" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -28553,7 +28549,7 @@
         </is>
       </c>
       <c r="N223" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -28566,7 +28562,7 @@
         </is>
       </c>
       <c r="Q223" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R223" s="2" t="inlineStr">
         <is>
@@ -28626,7 +28622,7 @@
         </is>
       </c>
       <c r="J224" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -28642,7 +28638,7 @@
         </is>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
@@ -28655,7 +28651,7 @@
         </is>
       </c>
       <c r="Q224" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R224" s="2" t="inlineStr">
         <is>
@@ -28715,7 +28711,7 @@
         </is>
       </c>
       <c r="J225" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -28731,7 +28727,7 @@
         </is>
       </c>
       <c r="N225" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -28744,7 +28740,7 @@
         </is>
       </c>
       <c r="Q225" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R225" s="2" t="inlineStr">
         <is>
@@ -28804,7 +28800,7 @@
         </is>
       </c>
       <c r="J226" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -28820,7 +28816,7 @@
         </is>
       </c>
       <c r="N226" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>
@@ -28833,7 +28829,7 @@
         </is>
       </c>
       <c r="Q226" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R226" s="2" t="inlineStr">
         <is>
@@ -28893,7 +28889,7 @@
         </is>
       </c>
       <c r="J227" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -28909,7 +28905,7 @@
         </is>
       </c>
       <c r="N227" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
@@ -28922,7 +28918,7 @@
         </is>
       </c>
       <c r="Q227" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R227" s="2" t="inlineStr">
         <is>
@@ -28982,7 +28978,7 @@
         </is>
       </c>
       <c r="J228" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -28998,7 +28994,7 @@
         </is>
       </c>
       <c r="N228" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O228" s="2" t="inlineStr">
         <is>
@@ -29011,7 +29007,7 @@
         </is>
       </c>
       <c r="Q228" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R228" s="2" t="inlineStr">
         <is>
@@ -29071,7 +29067,7 @@
         </is>
       </c>
       <c r="J229" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
@@ -29087,7 +29083,7 @@
         </is>
       </c>
       <c r="N229" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O229" s="2" t="inlineStr">
         <is>
@@ -29100,7 +29096,7 @@
         </is>
       </c>
       <c r="Q229" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R229" s="2" t="inlineStr">
         <is>
@@ -29229,7 +29225,7 @@
         </is>
       </c>
       <c r="J231" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -29245,7 +29241,7 @@
         </is>
       </c>
       <c r="N231" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O231" s="2" t="inlineStr">
         <is>
@@ -29258,7 +29254,7 @@
         </is>
       </c>
       <c r="Q231" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R231" s="2" t="inlineStr">
         <is>
@@ -29318,7 +29314,7 @@
         </is>
       </c>
       <c r="J232" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -29334,7 +29330,7 @@
         </is>
       </c>
       <c r="N232" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O232" s="2" t="inlineStr">
         <is>
@@ -29347,7 +29343,7 @@
         </is>
       </c>
       <c r="Q232" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R232" s="2" t="inlineStr">
         <is>
@@ -29407,7 +29403,7 @@
         </is>
       </c>
       <c r="J233" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -29423,7 +29419,7 @@
         </is>
       </c>
       <c r="N233" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O233" s="2" t="inlineStr">
         <is>
@@ -29436,7 +29432,7 @@
         </is>
       </c>
       <c r="Q233" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R233" s="2" t="inlineStr">
         <is>
@@ -29496,7 +29492,7 @@
         </is>
       </c>
       <c r="J234" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -29512,7 +29508,7 @@
         </is>
       </c>
       <c r="N234" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O234" s="2" t="inlineStr">
         <is>
@@ -29525,7 +29521,7 @@
         </is>
       </c>
       <c r="Q234" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R234" s="2" t="inlineStr">
         <is>
@@ -29585,7 +29581,7 @@
         </is>
       </c>
       <c r="J235" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -29601,7 +29597,7 @@
         </is>
       </c>
       <c r="N235" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O235" s="2" t="inlineStr">
         <is>
@@ -29614,7 +29610,7 @@
         </is>
       </c>
       <c r="Q235" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R235" s="2" t="inlineStr">
         <is>
@@ -29674,7 +29670,7 @@
         </is>
       </c>
       <c r="J236" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -29690,7 +29686,7 @@
         </is>
       </c>
       <c r="N236" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O236" s="2" t="inlineStr">
         <is>
@@ -29703,7 +29699,7 @@
         </is>
       </c>
       <c r="Q236" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R236" s="2" t="inlineStr">
         <is>
@@ -29763,7 +29759,7 @@
         </is>
       </c>
       <c r="J237" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -29779,7 +29775,7 @@
         </is>
       </c>
       <c r="N237" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O237" s="2" t="inlineStr">
         <is>
@@ -29792,7 +29788,7 @@
         </is>
       </c>
       <c r="Q237" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R237" s="2" t="inlineStr">
         <is>
@@ -29852,7 +29848,7 @@
         </is>
       </c>
       <c r="J238" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -29868,7 +29864,7 @@
         </is>
       </c>
       <c r="N238" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O238" s="2" t="inlineStr">
         <is>
@@ -29881,7 +29877,7 @@
         </is>
       </c>
       <c r="Q238" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R238" s="2" t="inlineStr">
         <is>
@@ -29941,7 +29937,7 @@
         </is>
       </c>
       <c r="J239" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -29957,7 +29953,7 @@
         </is>
       </c>
       <c r="N239" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O239" s="2" t="inlineStr">
         <is>
@@ -29970,7 +29966,7 @@
         </is>
       </c>
       <c r="Q239" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R239" s="2" t="inlineStr">
         <is>
@@ -30030,7 +30026,7 @@
         </is>
       </c>
       <c r="J240" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -30046,7 +30042,7 @@
         </is>
       </c>
       <c r="N240" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O240" s="2" t="inlineStr">
         <is>
@@ -30059,7 +30055,7 @@
         </is>
       </c>
       <c r="Q240" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R240" s="2" t="inlineStr">
         <is>
@@ -30119,7 +30115,7 @@
         </is>
       </c>
       <c r="J241" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
@@ -30135,7 +30131,7 @@
         </is>
       </c>
       <c r="N241" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O241" s="2" t="inlineStr">
         <is>
@@ -30148,7 +30144,7 @@
         </is>
       </c>
       <c r="Q241" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R241" s="2" t="inlineStr">
         <is>
